--- a/LULU/unbesiegbarmodel1.xlsx
+++ b/LULU/unbesiegbarmodel1.xlsx
@@ -1115,14 +1115,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="B2:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1130,7 +1129,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1145,7 +1143,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1153,7 +1150,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1182,7 +1178,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1206,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1247,7 +1241,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="11" t="inlineStr">
         <is>
@@ -1391,7 +1384,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1543,7 +1535,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1833,7 +1824,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1877,7 +1867,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2601,7 +2590,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4604,7 +4592,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4662,7 +4649,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4670,7 +4656,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -6571,7 +6556,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -7131,7 +7115,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7371,7 +7354,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7781,7 +7763,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -8180,7 +8161,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -8435,7 +8415,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -9439,7 +9418,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -11125,7 +11103,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -11396,8 +11373,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -11416,7 +11391,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -11477,7 +11451,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -11562,7 +11535,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -11683,7 +11655,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -11744,7 +11715,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -11836,7 +11806,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -11955,8 +11924,6 @@
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -12497,7 +12464,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -12915,7 +12881,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -13033,7 +12998,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -13100,7 +13064,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -13190,7 +13153,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -13367,7 +13329,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>
